--- a/models/demo-recycling/demo-recycling.xlsx
+++ b/models/demo-recycling/demo-recycling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/demo-recycling/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-recycling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C083FC-E838-C749-A6B8-67EF5410A89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EC7AC2-33D1-324C-9408-6832292F9390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14040" yWindow="600" windowWidth="37160" windowHeight="26900" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="14040" yWindow="600" windowWidth="37160" windowHeight="26880" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Inputs - Spatial" sheetId="4" r:id="rId4"/>
     <sheet name="Inputs - Advanced Curves" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,6 +44,7 @@
   <authors>
     <author>Magnan, Michael</author>
     <author>mhafer</author>
+    <author>tc={D05FF5F5-CA0B-B743-ABCF-B30F4C231AFF}</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{DE5AEED7-5306-0F41-A9F6-E09723C07087}">
@@ -380,27 +381,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G58" authorId="0" shapeId="0" xr:uid="{9D0C205B-9C9C-3F4A-912F-B707A4FF980A}">
+    <comment ref="G58" authorId="2" shapeId="0" xr:uid="{D05FF5F5-CA0B-B743-ABCF-B30F4C231AFF}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -767,18 +754,9 @@
     <t>Proportion</t>
   </si>
   <si>
-    <t>Target Amount (Double precison)</t>
-  </si>
-  <si>
     <t>New Physical State Name</t>
   </si>
   <si>
-    <t>Filter By Physical State Name/Group</t>
-  </si>
-  <si>
-    <t>Filter By Species Name/Group</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -1014,13 +992,22 @@
   </si>
   <si>
     <t>Cascading</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Physical State Rule</t>
+  </si>
+  <si>
+    <t>Species Rule</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1056,8 +1043,14 @@
       <name val="HelveticaNeue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1068,6 +1061,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1083,12 +1082,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1125,6 +1125,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Magnan, Michael" id="{A4D05BEF-4657-FF44-A8C6-FF0953D4F337}" userId="" providerId=""/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1442,6 +1448,15 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G58" personId="{A4D05BEF-4657-FF44-A8C6-FF0953D4F337}" id="{D05FF5F5-CA0B-B743-ABCF-B30F4C231AFF}">
+    <text xml:space="preserve">The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
   <dimension ref="B1:L97"/>
@@ -1522,7 +1537,7 @@
         <v>1725</v>
       </c>
       <c r="E4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="16" customHeight="1">
@@ -1538,7 +1553,7 @@
         <v>1725</v>
       </c>
       <c r="E5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="16" customHeight="1">
@@ -1554,7 +1569,7 @@
         <v>1725</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="16" customHeight="1">
@@ -1709,34 +1724,34 @@
     </row>
     <row r="23" spans="2:7" ht="16" customHeight="1">
       <c r="B23" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="16" customHeight="1">
       <c r="B24" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="16" customHeight="1">
       <c r="B25" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="16" customHeight="1">
       <c r="B26" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
@@ -2176,25 +2191,25 @@
       <c r="E58" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="16" customHeight="1">
       <c r="B60" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C60" t="str">
         <f>$C$53</f>
@@ -2218,7 +2233,7 @@
     </row>
     <row r="61" spans="2:10" ht="16" customHeight="1">
       <c r="B61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" ref="C61:C63" si="3">$C$53</f>
@@ -2242,7 +2257,7 @@
     </row>
     <row r="62" spans="2:10" ht="16" customHeight="1">
       <c r="B62" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="3"/>
@@ -2266,7 +2281,7 @@
     </row>
     <row r="63" spans="2:10" ht="16" customHeight="1">
       <c r="B63" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="3"/>
@@ -2290,7 +2305,7 @@
     </row>
     <row r="65" spans="2:9" ht="16" customHeight="1">
       <c r="B65" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C65" t="str">
         <f>$C$53</f>
@@ -2314,7 +2329,7 @@
     </row>
     <row r="66" spans="2:9" ht="16" customHeight="1">
       <c r="B66" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" ref="C66:C68" si="5">$C$53</f>
@@ -2338,7 +2353,7 @@
     </row>
     <row r="67" spans="2:9" ht="16" customHeight="1">
       <c r="B67" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="5"/>
@@ -2362,7 +2377,7 @@
     </row>
     <row r="68" spans="2:9" ht="16" customHeight="1">
       <c r="B68" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="5"/>
@@ -2386,7 +2401,7 @@
     </row>
     <row r="70" spans="2:9" ht="16" customHeight="1">
       <c r="B70" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C70" t="str">
         <f>$C$53</f>
@@ -2406,7 +2421,7 @@
     </row>
     <row r="71" spans="2:9" ht="16" customHeight="1">
       <c r="B71" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" ref="C71:C73" si="8">$C$53</f>
@@ -2426,7 +2441,7 @@
     </row>
     <row r="72" spans="2:9" ht="16" customHeight="1">
       <c r="B72" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="8"/>
@@ -2446,7 +2461,7 @@
     </row>
     <row r="73" spans="2:9" ht="16" customHeight="1">
       <c r="B73" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="8"/>
@@ -2466,7 +2481,7 @@
     </row>
     <row r="75" spans="2:9" ht="16" customHeight="1">
       <c r="B75" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C75" t="str">
         <f>C56</f>
@@ -2481,7 +2496,7 @@
     </row>
     <row r="77" spans="2:9" ht="16" customHeight="1">
       <c r="B77" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C77" t="str">
         <f>C54</f>
@@ -2496,7 +2511,7 @@
     </row>
     <row r="79" spans="2:9" ht="16" customHeight="1">
       <c r="B79" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C79" t="str">
         <f>$C$55</f>
@@ -2516,7 +2531,7 @@
     </row>
     <row r="80" spans="2:9" ht="16" customHeight="1">
       <c r="B80" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" ref="C80:C82" si="9">$C$55</f>
@@ -2536,7 +2551,7 @@
     </row>
     <row r="81" spans="2:8" ht="16" customHeight="1">
       <c r="B81" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="9"/>
@@ -2556,7 +2571,7 @@
     </row>
     <row r="82" spans="2:8" ht="16" customHeight="1">
       <c r="B82" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="9"/>
@@ -2577,7 +2592,7 @@
     </row>
     <row r="84" spans="2:8" ht="16" customHeight="1">
       <c r="B84" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C84" t="str">
         <f>$C$55</f>
@@ -2597,7 +2612,7 @@
     </row>
     <row r="85" spans="2:8" ht="16" customHeight="1">
       <c r="B85" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" ref="C85:C87" si="10">$C$55</f>
@@ -2617,7 +2632,7 @@
     </row>
     <row r="86" spans="2:8" ht="16" customHeight="1">
       <c r="B86" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="10"/>
@@ -2637,7 +2652,7 @@
     </row>
     <row r="87" spans="2:8" ht="16" customHeight="1">
       <c r="B87" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="10"/>
@@ -2658,7 +2673,7 @@
     </row>
     <row r="89" spans="2:8" ht="16" customHeight="1">
       <c r="B89" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C89" t="str">
         <f>$C$55</f>
@@ -2678,7 +2693,7 @@
     </row>
     <row r="90" spans="2:8" ht="16" customHeight="1">
       <c r="B90" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" ref="C90:C92" si="11">$C$55</f>
@@ -2698,7 +2713,7 @@
     </row>
     <row r="91" spans="2:8" ht="16" customHeight="1">
       <c r="B91" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="11"/>
@@ -2718,7 +2733,7 @@
     </row>
     <row r="92" spans="2:8" ht="16" customHeight="1">
       <c r="B92" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="11"/>
@@ -2739,7 +2754,7 @@
     </row>
     <row r="94" spans="2:8" ht="16" customHeight="1">
       <c r="B94" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C94" t="str">
         <f>$C$55</f>
@@ -2755,7 +2770,7 @@
     </row>
     <row r="95" spans="2:8" ht="16" customHeight="1">
       <c r="B95" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" ref="C95:C97" si="12">$C$55</f>
@@ -2771,7 +2786,7 @@
     </row>
     <row r="96" spans="2:8" ht="16" customHeight="1">
       <c r="B96" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="12"/>
@@ -2787,7 +2802,7 @@
     </row>
     <row r="97" spans="2:5" ht="16" customHeight="1">
       <c r="B97" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="12"/>
@@ -2825,31 +2840,31 @@
   <sheetData>
     <row r="1" spans="2:11" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>34</v>
@@ -2857,7 +2872,7 @@
     </row>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2879,7 +2894,7 @@
     </row>
     <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2921,58 +2936,58 @@
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1">
       <c r="B9" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1</v>
@@ -2986,27 +3001,27 @@
     </row>
     <row r="11" spans="2:7" s="3" customFormat="1">
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="2:7" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>33</v>
@@ -3017,23 +3032,23 @@
     </row>
     <row r="15" spans="2:7">
       <c r="B15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="2:5" s="3" customFormat="1">
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>1</v>
@@ -3047,24 +3062,24 @@
     </row>
     <row r="20" spans="2:5" s="3" customFormat="1">
       <c r="B20" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:5" s="3" customFormat="1">
       <c r="B22" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>34</v>
@@ -3094,22 +3109,22 @@
   <sheetData>
     <row r="1" spans="2:8" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
@@ -3117,13 +3132,13 @@
     </row>
     <row r="2" spans="2:8">
       <c r="B2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>1725</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E2">
         <v>998</v>
@@ -3131,7 +3146,7 @@
     </row>
     <row r="5" spans="2:8" s="3" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
@@ -3139,21 +3154,21 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="3" customFormat="1">
       <c r="B8" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>34</v>
@@ -3161,10 +3176,10 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D10" t="str">
         <f>C6</f>
@@ -3173,21 +3188,21 @@
     </row>
     <row r="13" spans="2:8" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" t="str">
         <f>C10</f>
@@ -3219,13 +3234,13 @@
   <sheetData>
     <row r="1" spans="2:6" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>33</v>
@@ -3236,21 +3251,21 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="2:6" s="3" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
@@ -3264,32 +3279,32 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="2:6" s="3" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C14" t="str">
         <f>C9</f>
@@ -3308,21 +3323,21 @@
     </row>
     <row r="19" spans="2:5" s="3" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C21" t="str">
         <f>$C$3</f>
@@ -3337,7 +3352,7 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" ref="C22:C85" si="0">$C$3</f>
@@ -3352,7 +3367,7 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -3367,7 +3382,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -3382,7 +3397,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -3397,7 +3412,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -3412,7 +3427,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -3427,7 +3442,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -3442,7 +3457,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -3457,7 +3472,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -3472,7 +3487,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -3487,7 +3502,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -3502,7 +3517,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -3517,7 +3532,7 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -3532,7 +3547,7 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -3547,7 +3562,7 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -3562,7 +3577,7 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -3577,7 +3592,7 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -3592,7 +3607,7 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -3607,7 +3622,7 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -3622,7 +3637,7 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -3637,7 +3652,7 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
@@ -3652,7 +3667,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
@@ -3667,7 +3682,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
@@ -3682,7 +3697,7 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
@@ -3697,7 +3712,7 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
@@ -3712,7 +3727,7 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
@@ -3727,7 +3742,7 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
@@ -3742,7 +3757,7 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
@@ -3757,7 +3772,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
@@ -3772,7 +3787,7 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
@@ -3787,7 +3802,7 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
@@ -3802,7 +3817,7 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
@@ -3817,7 +3832,7 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -3832,7 +3847,7 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -3847,7 +3862,7 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -3862,7 +3877,7 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -3877,7 +3892,7 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -3892,7 +3907,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
@@ -3907,7 +3922,7 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
@@ -3922,7 +3937,7 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
@@ -3937,7 +3952,7 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
@@ -3952,7 +3967,7 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
@@ -3967,7 +3982,7 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
@@ -3982,7 +3997,7 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="0"/>
@@ -3997,7 +4012,7 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="0"/>
@@ -4012,7 +4027,7 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="0"/>
@@ -4027,7 +4042,7 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="0"/>
@@ -4042,7 +4057,7 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="0"/>
@@ -4057,7 +4072,7 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="0"/>
@@ -4072,7 +4087,7 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="0"/>
@@ -4087,7 +4102,7 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="0"/>
@@ -4102,7 +4117,7 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="0"/>
@@ -4117,7 +4132,7 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="0"/>
@@ -4132,7 +4147,7 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="0"/>
@@ -4147,7 +4162,7 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="0"/>
@@ -4162,7 +4177,7 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="0"/>
@@ -4177,7 +4192,7 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="0"/>
@@ -4192,7 +4207,7 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="0"/>
@@ -4207,7 +4222,7 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="0"/>
@@ -4222,7 +4237,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="0"/>
@@ -4237,7 +4252,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="0"/>
@@ -4252,7 +4267,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="0"/>
@@ -4267,7 +4282,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="0"/>
@@ -4282,7 +4297,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="0"/>
@@ -4297,7 +4312,7 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" ref="C86:C149" si="1">$C$3</f>
@@ -4312,7 +4327,7 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="1"/>
@@ -4327,7 +4342,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="1"/>
@@ -4342,7 +4357,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="1"/>
@@ -4357,7 +4372,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
@@ -4372,7 +4387,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
@@ -4387,7 +4402,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
@@ -4402,7 +4417,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
@@ -4417,7 +4432,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
@@ -4432,7 +4447,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
@@ -4447,7 +4462,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
@@ -4462,7 +4477,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
@@ -4477,7 +4492,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
@@ -4492,7 +4507,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
@@ -4507,7 +4522,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
@@ -4522,7 +4537,7 @@
     </row>
     <row r="101" spans="2:5">
       <c r="B101" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
@@ -4537,7 +4552,7 @@
     </row>
     <row r="102" spans="2:5">
       <c r="B102" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
@@ -4552,7 +4567,7 @@
     </row>
     <row r="103" spans="2:5">
       <c r="B103" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
@@ -4567,7 +4582,7 @@
     </row>
     <row r="104" spans="2:5">
       <c r="B104" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
@@ -4582,7 +4597,7 @@
     </row>
     <row r="105" spans="2:5">
       <c r="B105" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
@@ -4597,7 +4612,7 @@
     </row>
     <row r="106" spans="2:5">
       <c r="B106" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
@@ -4612,7 +4627,7 @@
     </row>
     <row r="107" spans="2:5">
       <c r="B107" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
@@ -4627,7 +4642,7 @@
     </row>
     <row r="108" spans="2:5">
       <c r="B108" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
@@ -4642,7 +4657,7 @@
     </row>
     <row r="109" spans="2:5">
       <c r="B109" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
@@ -4657,7 +4672,7 @@
     </row>
     <row r="110" spans="2:5">
       <c r="B110" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
@@ -4672,7 +4687,7 @@
     </row>
     <row r="111" spans="2:5">
       <c r="B111" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
@@ -4687,7 +4702,7 @@
     </row>
     <row r="112" spans="2:5">
       <c r="B112" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
@@ -4702,7 +4717,7 @@
     </row>
     <row r="113" spans="2:5">
       <c r="B113" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
@@ -4717,7 +4732,7 @@
     </row>
     <row r="114" spans="2:5">
       <c r="B114" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
@@ -4732,7 +4747,7 @@
     </row>
     <row r="115" spans="2:5">
       <c r="B115" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
@@ -4747,7 +4762,7 @@
     </row>
     <row r="116" spans="2:5">
       <c r="B116" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
@@ -4762,7 +4777,7 @@
     </row>
     <row r="117" spans="2:5">
       <c r="B117" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
@@ -4777,7 +4792,7 @@
     </row>
     <row r="118" spans="2:5">
       <c r="B118" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
@@ -4792,7 +4807,7 @@
     </row>
     <row r="119" spans="2:5">
       <c r="B119" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
@@ -4807,7 +4822,7 @@
     </row>
     <row r="120" spans="2:5">
       <c r="B120" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
@@ -4822,7 +4837,7 @@
     </row>
     <row r="121" spans="2:5">
       <c r="B121" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
@@ -4837,7 +4852,7 @@
     </row>
     <row r="122" spans="2:5">
       <c r="B122" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
@@ -4852,7 +4867,7 @@
     </row>
     <row r="123" spans="2:5">
       <c r="B123" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
@@ -4867,7 +4882,7 @@
     </row>
     <row r="124" spans="2:5">
       <c r="B124" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
@@ -4882,7 +4897,7 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
@@ -4897,7 +4912,7 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
@@ -4912,7 +4927,7 @@
     </row>
     <row r="127" spans="2:5">
       <c r="B127" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
@@ -4927,7 +4942,7 @@
     </row>
     <row r="128" spans="2:5">
       <c r="B128" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
@@ -4942,7 +4957,7 @@
     </row>
     <row r="129" spans="2:5">
       <c r="B129" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="1"/>
@@ -4957,7 +4972,7 @@
     </row>
     <row r="130" spans="2:5">
       <c r="B130" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="1"/>
@@ -4972,7 +4987,7 @@
     </row>
     <row r="131" spans="2:5">
       <c r="B131" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="1"/>
@@ -4987,7 +5002,7 @@
     </row>
     <row r="132" spans="2:5">
       <c r="B132" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="1"/>
@@ -5002,7 +5017,7 @@
     </row>
     <row r="133" spans="2:5">
       <c r="B133" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="1"/>
@@ -5017,7 +5032,7 @@
     </row>
     <row r="134" spans="2:5">
       <c r="B134" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="1"/>
@@ -5032,7 +5047,7 @@
     </row>
     <row r="135" spans="2:5">
       <c r="B135" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="1"/>
@@ -5047,7 +5062,7 @@
     </row>
     <row r="136" spans="2:5">
       <c r="B136" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="1"/>
@@ -5062,7 +5077,7 @@
     </row>
     <row r="137" spans="2:5">
       <c r="B137" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="1"/>
@@ -5077,7 +5092,7 @@
     </row>
     <row r="138" spans="2:5">
       <c r="B138" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="1"/>
@@ -5092,7 +5107,7 @@
     </row>
     <row r="139" spans="2:5">
       <c r="B139" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="1"/>
@@ -5107,7 +5122,7 @@
     </row>
     <row r="140" spans="2:5">
       <c r="B140" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="1"/>
@@ -5122,7 +5137,7 @@
     </row>
     <row r="141" spans="2:5">
       <c r="B141" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="1"/>
@@ -5137,7 +5152,7 @@
     </row>
     <row r="142" spans="2:5">
       <c r="B142" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="1"/>
@@ -5152,7 +5167,7 @@
     </row>
     <row r="143" spans="2:5">
       <c r="B143" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="1"/>
@@ -5167,7 +5182,7 @@
     </row>
     <row r="144" spans="2:5">
       <c r="B144" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C144" t="str">
         <f t="shared" si="1"/>
@@ -5182,7 +5197,7 @@
     </row>
     <row r="145" spans="2:5">
       <c r="B145" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C145" t="str">
         <f t="shared" si="1"/>
@@ -5197,7 +5212,7 @@
     </row>
     <row r="146" spans="2:5">
       <c r="B146" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C146" t="str">
         <f t="shared" si="1"/>
@@ -5212,7 +5227,7 @@
     </row>
     <row r="147" spans="2:5">
       <c r="B147" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C147" t="str">
         <f t="shared" si="1"/>
@@ -5227,7 +5242,7 @@
     </row>
     <row r="148" spans="2:5">
       <c r="B148" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C148" t="str">
         <f t="shared" si="1"/>
@@ -5242,7 +5257,7 @@
     </row>
     <row r="149" spans="2:5">
       <c r="B149" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C149" t="str">
         <f t="shared" si="1"/>
@@ -5257,7 +5272,7 @@
     </row>
     <row r="150" spans="2:5">
       <c r="B150" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C150" t="str">
         <f t="shared" ref="C150:C213" si="2">$C$3</f>
@@ -5272,7 +5287,7 @@
     </row>
     <row r="151" spans="2:5">
       <c r="B151" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C151" t="str">
         <f t="shared" si="2"/>
@@ -5287,7 +5302,7 @@
     </row>
     <row r="152" spans="2:5">
       <c r="B152" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C152" t="str">
         <f t="shared" si="2"/>
@@ -5302,7 +5317,7 @@
     </row>
     <row r="153" spans="2:5">
       <c r="B153" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C153" t="str">
         <f t="shared" si="2"/>
@@ -5317,7 +5332,7 @@
     </row>
     <row r="154" spans="2:5">
       <c r="B154" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C154" t="str">
         <f t="shared" si="2"/>
@@ -5332,7 +5347,7 @@
     </row>
     <row r="155" spans="2:5">
       <c r="B155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C155" t="str">
         <f t="shared" si="2"/>
@@ -5347,7 +5362,7 @@
     </row>
     <row r="156" spans="2:5">
       <c r="B156" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C156" t="str">
         <f t="shared" si="2"/>
@@ -5362,7 +5377,7 @@
     </row>
     <row r="157" spans="2:5">
       <c r="B157" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C157" t="str">
         <f t="shared" si="2"/>
@@ -5377,7 +5392,7 @@
     </row>
     <row r="158" spans="2:5">
       <c r="B158" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C158" t="str">
         <f t="shared" si="2"/>
@@ -5392,7 +5407,7 @@
     </row>
     <row r="159" spans="2:5">
       <c r="B159" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C159" t="str">
         <f t="shared" si="2"/>
@@ -5407,7 +5422,7 @@
     </row>
     <row r="160" spans="2:5">
       <c r="B160" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C160" t="str">
         <f t="shared" si="2"/>
@@ -5422,7 +5437,7 @@
     </row>
     <row r="161" spans="2:5">
       <c r="B161" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C161" t="str">
         <f t="shared" si="2"/>
@@ -5437,7 +5452,7 @@
     </row>
     <row r="162" spans="2:5">
       <c r="B162" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C162" t="str">
         <f t="shared" si="2"/>
@@ -5452,7 +5467,7 @@
     </row>
     <row r="163" spans="2:5">
       <c r="B163" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C163" t="str">
         <f t="shared" si="2"/>
@@ -5467,7 +5482,7 @@
     </row>
     <row r="164" spans="2:5">
       <c r="B164" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C164" t="str">
         <f t="shared" si="2"/>
@@ -5482,7 +5497,7 @@
     </row>
     <row r="165" spans="2:5">
       <c r="B165" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C165" t="str">
         <f t="shared" si="2"/>
@@ -5497,7 +5512,7 @@
     </row>
     <row r="166" spans="2:5">
       <c r="B166" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C166" t="str">
         <f t="shared" si="2"/>
@@ -5512,7 +5527,7 @@
     </row>
     <row r="167" spans="2:5">
       <c r="B167" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C167" t="str">
         <f t="shared" si="2"/>
@@ -5527,7 +5542,7 @@
     </row>
     <row r="168" spans="2:5">
       <c r="B168" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C168" t="str">
         <f t="shared" si="2"/>
@@ -5542,7 +5557,7 @@
     </row>
     <row r="169" spans="2:5">
       <c r="B169" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C169" t="str">
         <f t="shared" si="2"/>
@@ -5557,7 +5572,7 @@
     </row>
     <row r="170" spans="2:5">
       <c r="B170" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C170" t="str">
         <f t="shared" si="2"/>
@@ -5572,7 +5587,7 @@
     </row>
     <row r="171" spans="2:5">
       <c r="B171" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C171" t="str">
         <f t="shared" si="2"/>
@@ -5587,7 +5602,7 @@
     </row>
     <row r="172" spans="2:5">
       <c r="B172" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C172" t="str">
         <f t="shared" si="2"/>
@@ -5602,7 +5617,7 @@
     </row>
     <row r="173" spans="2:5">
       <c r="B173" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C173" t="str">
         <f t="shared" si="2"/>
@@ -5617,7 +5632,7 @@
     </row>
     <row r="174" spans="2:5">
       <c r="B174" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C174" t="str">
         <f t="shared" si="2"/>
@@ -5632,7 +5647,7 @@
     </row>
     <row r="175" spans="2:5">
       <c r="B175" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="2"/>
@@ -5647,7 +5662,7 @@
     </row>
     <row r="176" spans="2:5">
       <c r="B176" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="2"/>
@@ -5662,7 +5677,7 @@
     </row>
     <row r="177" spans="2:5">
       <c r="B177" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="2"/>
@@ -5677,7 +5692,7 @@
     </row>
     <row r="178" spans="2:5">
       <c r="B178" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C178" t="str">
         <f t="shared" si="2"/>
@@ -5692,7 +5707,7 @@
     </row>
     <row r="179" spans="2:5">
       <c r="B179" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C179" t="str">
         <f t="shared" si="2"/>
@@ -5707,7 +5722,7 @@
     </row>
     <row r="180" spans="2:5">
       <c r="B180" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="2"/>
@@ -5722,7 +5737,7 @@
     </row>
     <row r="181" spans="2:5">
       <c r="B181" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C181" t="str">
         <f t="shared" si="2"/>
@@ -5737,7 +5752,7 @@
     </row>
     <row r="182" spans="2:5">
       <c r="B182" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C182" t="str">
         <f t="shared" si="2"/>
@@ -5752,7 +5767,7 @@
     </row>
     <row r="183" spans="2:5">
       <c r="B183" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C183" t="str">
         <f t="shared" si="2"/>
@@ -5767,7 +5782,7 @@
     </row>
     <row r="184" spans="2:5">
       <c r="B184" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="2"/>
@@ -5782,7 +5797,7 @@
     </row>
     <row r="185" spans="2:5">
       <c r="B185" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C185" t="str">
         <f t="shared" si="2"/>
@@ -5797,7 +5812,7 @@
     </row>
     <row r="186" spans="2:5">
       <c r="B186" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C186" t="str">
         <f t="shared" si="2"/>
@@ -5812,7 +5827,7 @@
     </row>
     <row r="187" spans="2:5">
       <c r="B187" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="2"/>
@@ -5827,7 +5842,7 @@
     </row>
     <row r="188" spans="2:5">
       <c r="B188" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="2"/>
@@ -5842,7 +5857,7 @@
     </row>
     <row r="189" spans="2:5">
       <c r="B189" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C189" t="str">
         <f t="shared" si="2"/>
@@ -5857,7 +5872,7 @@
     </row>
     <row r="190" spans="2:5">
       <c r="B190" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C190" t="str">
         <f t="shared" si="2"/>
@@ -5872,7 +5887,7 @@
     </row>
     <row r="191" spans="2:5">
       <c r="B191" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C191" t="str">
         <f t="shared" si="2"/>
@@ -5887,7 +5902,7 @@
     </row>
     <row r="192" spans="2:5">
       <c r="B192" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C192" t="str">
         <f t="shared" si="2"/>
@@ -5902,7 +5917,7 @@
     </row>
     <row r="193" spans="2:5">
       <c r="B193" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C193" t="str">
         <f t="shared" si="2"/>
@@ -5917,7 +5932,7 @@
     </row>
     <row r="194" spans="2:5">
       <c r="B194" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C194" t="str">
         <f t="shared" si="2"/>
@@ -5932,7 +5947,7 @@
     </row>
     <row r="195" spans="2:5">
       <c r="B195" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C195" t="str">
         <f t="shared" si="2"/>
@@ -5947,7 +5962,7 @@
     </row>
     <row r="196" spans="2:5">
       <c r="B196" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C196" t="str">
         <f t="shared" si="2"/>
@@ -5962,7 +5977,7 @@
     </row>
     <row r="197" spans="2:5">
       <c r="B197" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C197" t="str">
         <f t="shared" si="2"/>
@@ -5977,7 +5992,7 @@
     </row>
     <row r="198" spans="2:5">
       <c r="B198" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C198" t="str">
         <f t="shared" si="2"/>
@@ -5992,7 +6007,7 @@
     </row>
     <row r="199" spans="2:5">
       <c r="B199" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C199" t="str">
         <f t="shared" si="2"/>
@@ -6007,7 +6022,7 @@
     </row>
     <row r="200" spans="2:5">
       <c r="B200" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C200" t="str">
         <f t="shared" si="2"/>
@@ -6022,7 +6037,7 @@
     </row>
     <row r="201" spans="2:5">
       <c r="B201" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C201" t="str">
         <f t="shared" si="2"/>
@@ -6037,7 +6052,7 @@
     </row>
     <row r="202" spans="2:5">
       <c r="B202" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C202" t="str">
         <f t="shared" si="2"/>
@@ -6052,7 +6067,7 @@
     </row>
     <row r="203" spans="2:5">
       <c r="B203" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C203" t="str">
         <f t="shared" si="2"/>
@@ -6067,7 +6082,7 @@
     </row>
     <row r="204" spans="2:5">
       <c r="B204" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C204" t="str">
         <f t="shared" si="2"/>
@@ -6082,7 +6097,7 @@
     </row>
     <row r="205" spans="2:5">
       <c r="B205" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C205" t="str">
         <f t="shared" si="2"/>
@@ -6097,7 +6112,7 @@
     </row>
     <row r="206" spans="2:5">
       <c r="B206" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C206" t="str">
         <f t="shared" si="2"/>
@@ -6112,7 +6127,7 @@
     </row>
     <row r="207" spans="2:5">
       <c r="B207" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C207" t="str">
         <f t="shared" si="2"/>
@@ -6127,7 +6142,7 @@
     </row>
     <row r="208" spans="2:5">
       <c r="B208" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C208" t="str">
         <f t="shared" si="2"/>
@@ -6142,7 +6157,7 @@
     </row>
     <row r="209" spans="2:5">
       <c r="B209" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C209" t="str">
         <f t="shared" si="2"/>
@@ -6157,7 +6172,7 @@
     </row>
     <row r="210" spans="2:5">
       <c r="B210" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C210" t="str">
         <f t="shared" si="2"/>
@@ -6172,7 +6187,7 @@
     </row>
     <row r="211" spans="2:5">
       <c r="B211" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C211" t="str">
         <f t="shared" si="2"/>
@@ -6187,7 +6202,7 @@
     </row>
     <row r="212" spans="2:5">
       <c r="B212" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C212" t="str">
         <f t="shared" si="2"/>
@@ -6202,7 +6217,7 @@
     </row>
     <row r="213" spans="2:5">
       <c r="B213" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C213" t="str">
         <f t="shared" si="2"/>
@@ -6217,7 +6232,7 @@
     </row>
     <row r="214" spans="2:5">
       <c r="B214" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C214" t="str">
         <f t="shared" ref="C214:C277" si="3">$C$3</f>
@@ -6232,7 +6247,7 @@
     </row>
     <row r="215" spans="2:5">
       <c r="B215" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C215" t="str">
         <f t="shared" si="3"/>
@@ -6247,7 +6262,7 @@
     </row>
     <row r="216" spans="2:5">
       <c r="B216" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C216" t="str">
         <f t="shared" si="3"/>
@@ -6262,7 +6277,7 @@
     </row>
     <row r="217" spans="2:5">
       <c r="B217" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C217" t="str">
         <f t="shared" si="3"/>
@@ -6277,7 +6292,7 @@
     </row>
     <row r="218" spans="2:5">
       <c r="B218" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C218" t="str">
         <f t="shared" si="3"/>
@@ -6292,7 +6307,7 @@
     </row>
     <row r="219" spans="2:5">
       <c r="B219" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C219" t="str">
         <f t="shared" si="3"/>
@@ -6307,7 +6322,7 @@
     </row>
     <row r="220" spans="2:5">
       <c r="B220" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C220" t="str">
         <f t="shared" si="3"/>
@@ -6322,7 +6337,7 @@
     </row>
     <row r="221" spans="2:5">
       <c r="B221" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C221" t="str">
         <f t="shared" si="3"/>
@@ -6337,7 +6352,7 @@
     </row>
     <row r="222" spans="2:5">
       <c r="B222" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C222" t="str">
         <f t="shared" si="3"/>
@@ -6352,7 +6367,7 @@
     </row>
     <row r="223" spans="2:5">
       <c r="B223" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C223" t="str">
         <f t="shared" si="3"/>
@@ -6367,7 +6382,7 @@
     </row>
     <row r="224" spans="2:5">
       <c r="B224" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C224" t="str">
         <f t="shared" si="3"/>
@@ -6382,7 +6397,7 @@
     </row>
     <row r="225" spans="2:5">
       <c r="B225" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C225" t="str">
         <f t="shared" si="3"/>
@@ -6397,7 +6412,7 @@
     </row>
     <row r="226" spans="2:5">
       <c r="B226" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C226" t="str">
         <f t="shared" si="3"/>
@@ -6412,7 +6427,7 @@
     </row>
     <row r="227" spans="2:5">
       <c r="B227" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C227" t="str">
         <f t="shared" si="3"/>
@@ -6427,7 +6442,7 @@
     </row>
     <row r="228" spans="2:5">
       <c r="B228" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C228" t="str">
         <f t="shared" si="3"/>
@@ -6442,7 +6457,7 @@
     </row>
     <row r="229" spans="2:5">
       <c r="B229" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C229" t="str">
         <f t="shared" si="3"/>
@@ -6457,7 +6472,7 @@
     </row>
     <row r="230" spans="2:5">
       <c r="B230" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C230" t="str">
         <f t="shared" si="3"/>
@@ -6472,7 +6487,7 @@
     </row>
     <row r="231" spans="2:5">
       <c r="B231" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C231" t="str">
         <f t="shared" si="3"/>
@@ -6487,7 +6502,7 @@
     </row>
     <row r="232" spans="2:5">
       <c r="B232" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C232" t="str">
         <f t="shared" si="3"/>
@@ -6502,7 +6517,7 @@
     </row>
     <row r="233" spans="2:5">
       <c r="B233" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C233" t="str">
         <f t="shared" si="3"/>
@@ -6517,7 +6532,7 @@
     </row>
     <row r="234" spans="2:5">
       <c r="B234" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C234" t="str">
         <f t="shared" si="3"/>
@@ -6532,7 +6547,7 @@
     </row>
     <row r="235" spans="2:5">
       <c r="B235" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C235" t="str">
         <f t="shared" si="3"/>
@@ -6547,7 +6562,7 @@
     </row>
     <row r="236" spans="2:5">
       <c r="B236" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C236" t="str">
         <f t="shared" si="3"/>
@@ -6562,7 +6577,7 @@
     </row>
     <row r="237" spans="2:5">
       <c r="B237" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C237" t="str">
         <f t="shared" si="3"/>
@@ -6577,7 +6592,7 @@
     </row>
     <row r="238" spans="2:5">
       <c r="B238" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C238" t="str">
         <f t="shared" si="3"/>
@@ -6592,7 +6607,7 @@
     </row>
     <row r="239" spans="2:5">
       <c r="B239" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C239" t="str">
         <f t="shared" si="3"/>
@@ -6607,7 +6622,7 @@
     </row>
     <row r="240" spans="2:5">
       <c r="B240" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C240" t="str">
         <f t="shared" si="3"/>
@@ -6622,7 +6637,7 @@
     </row>
     <row r="241" spans="2:5">
       <c r="B241" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C241" t="str">
         <f t="shared" si="3"/>
@@ -6637,7 +6652,7 @@
     </row>
     <row r="242" spans="2:5">
       <c r="B242" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C242" t="str">
         <f t="shared" si="3"/>
@@ -6652,7 +6667,7 @@
     </row>
     <row r="243" spans="2:5">
       <c r="B243" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C243" t="str">
         <f t="shared" si="3"/>
@@ -6667,7 +6682,7 @@
     </row>
     <row r="244" spans="2:5">
       <c r="B244" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C244" t="str">
         <f t="shared" si="3"/>
@@ -6682,7 +6697,7 @@
     </row>
     <row r="245" spans="2:5">
       <c r="B245" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C245" t="str">
         <f t="shared" si="3"/>
@@ -6697,7 +6712,7 @@
     </row>
     <row r="246" spans="2:5">
       <c r="B246" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C246" t="str">
         <f t="shared" si="3"/>
@@ -6712,7 +6727,7 @@
     </row>
     <row r="247" spans="2:5">
       <c r="B247" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C247" t="str">
         <f t="shared" si="3"/>
@@ -6727,7 +6742,7 @@
     </row>
     <row r="248" spans="2:5">
       <c r="B248" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C248" t="str">
         <f t="shared" si="3"/>
@@ -6742,7 +6757,7 @@
     </row>
     <row r="249" spans="2:5">
       <c r="B249" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C249" t="str">
         <f t="shared" si="3"/>
@@ -6757,7 +6772,7 @@
     </row>
     <row r="250" spans="2:5">
       <c r="B250" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C250" t="str">
         <f t="shared" si="3"/>
@@ -6772,7 +6787,7 @@
     </row>
     <row r="251" spans="2:5">
       <c r="B251" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C251" t="str">
         <f t="shared" si="3"/>
@@ -6787,7 +6802,7 @@
     </row>
     <row r="252" spans="2:5">
       <c r="B252" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C252" t="str">
         <f t="shared" si="3"/>
@@ -6802,7 +6817,7 @@
     </row>
     <row r="253" spans="2:5">
       <c r="B253" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C253" t="str">
         <f t="shared" si="3"/>
@@ -6817,7 +6832,7 @@
     </row>
     <row r="254" spans="2:5">
       <c r="B254" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C254" t="str">
         <f t="shared" si="3"/>
@@ -6832,7 +6847,7 @@
     </row>
     <row r="255" spans="2:5">
       <c r="B255" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C255" t="str">
         <f t="shared" si="3"/>
@@ -6847,7 +6862,7 @@
     </row>
     <row r="256" spans="2:5">
       <c r="B256" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C256" t="str">
         <f t="shared" si="3"/>
@@ -6862,7 +6877,7 @@
     </row>
     <row r="257" spans="2:5">
       <c r="B257" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" si="3"/>
@@ -6877,7 +6892,7 @@
     </row>
     <row r="258" spans="2:5">
       <c r="B258" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C258" t="str">
         <f t="shared" si="3"/>
@@ -6892,7 +6907,7 @@
     </row>
     <row r="259" spans="2:5">
       <c r="B259" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C259" t="str">
         <f t="shared" si="3"/>
@@ -6907,7 +6922,7 @@
     </row>
     <row r="260" spans="2:5">
       <c r="B260" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C260" t="str">
         <f t="shared" si="3"/>
@@ -6922,7 +6937,7 @@
     </row>
     <row r="261" spans="2:5">
       <c r="B261" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C261" t="str">
         <f t="shared" si="3"/>
@@ -6937,7 +6952,7 @@
     </row>
     <row r="262" spans="2:5">
       <c r="B262" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C262" t="str">
         <f t="shared" si="3"/>
@@ -6952,7 +6967,7 @@
     </row>
     <row r="263" spans="2:5">
       <c r="B263" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C263" t="str">
         <f t="shared" si="3"/>
@@ -6967,7 +6982,7 @@
     </row>
     <row r="264" spans="2:5">
       <c r="B264" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C264" t="str">
         <f t="shared" si="3"/>
@@ -6982,7 +6997,7 @@
     </row>
     <row r="265" spans="2:5">
       <c r="B265" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C265" t="str">
         <f t="shared" si="3"/>
@@ -6997,7 +7012,7 @@
     </row>
     <row r="266" spans="2:5">
       <c r="B266" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C266" t="str">
         <f t="shared" si="3"/>
@@ -7012,7 +7027,7 @@
     </row>
     <row r="267" spans="2:5">
       <c r="B267" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C267" t="str">
         <f t="shared" si="3"/>
@@ -7027,7 +7042,7 @@
     </row>
     <row r="268" spans="2:5">
       <c r="B268" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C268" t="str">
         <f t="shared" si="3"/>
@@ -7042,7 +7057,7 @@
     </row>
     <row r="269" spans="2:5">
       <c r="B269" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C269" t="str">
         <f t="shared" si="3"/>
@@ -7057,7 +7072,7 @@
     </row>
     <row r="270" spans="2:5">
       <c r="B270" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C270" t="str">
         <f t="shared" si="3"/>
@@ -7072,7 +7087,7 @@
     </row>
     <row r="271" spans="2:5">
       <c r="B271" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C271" t="str">
         <f t="shared" si="3"/>
@@ -7087,7 +7102,7 @@
     </row>
     <row r="272" spans="2:5">
       <c r="B272" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C272" t="str">
         <f t="shared" si="3"/>
@@ -7102,7 +7117,7 @@
     </row>
     <row r="273" spans="2:5">
       <c r="B273" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C273" t="str">
         <f t="shared" si="3"/>
@@ -7117,7 +7132,7 @@
     </row>
     <row r="274" spans="2:5">
       <c r="B274" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C274" t="str">
         <f t="shared" si="3"/>
@@ -7132,7 +7147,7 @@
     </row>
     <row r="275" spans="2:5">
       <c r="B275" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C275" t="str">
         <f t="shared" si="3"/>
@@ -7147,7 +7162,7 @@
     </row>
     <row r="276" spans="2:5">
       <c r="B276" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C276" t="str">
         <f t="shared" si="3"/>
@@ -7162,7 +7177,7 @@
     </row>
     <row r="277" spans="2:5">
       <c r="B277" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C277" t="str">
         <f t="shared" si="3"/>
@@ -7177,7 +7192,7 @@
     </row>
     <row r="278" spans="2:5">
       <c r="B278" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C278" t="str">
         <f t="shared" ref="C278:C321" si="4">$C$3</f>
@@ -7192,7 +7207,7 @@
     </row>
     <row r="279" spans="2:5">
       <c r="B279" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C279" t="str">
         <f t="shared" si="4"/>
@@ -7207,7 +7222,7 @@
     </row>
     <row r="280" spans="2:5">
       <c r="B280" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C280" t="str">
         <f t="shared" si="4"/>
@@ -7222,7 +7237,7 @@
     </row>
     <row r="281" spans="2:5">
       <c r="B281" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C281" t="str">
         <f t="shared" si="4"/>
@@ -7237,7 +7252,7 @@
     </row>
     <row r="282" spans="2:5">
       <c r="B282" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C282" t="str">
         <f t="shared" si="4"/>
@@ -7252,7 +7267,7 @@
     </row>
     <row r="283" spans="2:5">
       <c r="B283" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C283" t="str">
         <f t="shared" si="4"/>
@@ -7267,7 +7282,7 @@
     </row>
     <row r="284" spans="2:5">
       <c r="B284" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C284" t="str">
         <f t="shared" si="4"/>
@@ -7282,7 +7297,7 @@
     </row>
     <row r="285" spans="2:5">
       <c r="B285" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C285" t="str">
         <f t="shared" si="4"/>
@@ -7297,7 +7312,7 @@
     </row>
     <row r="286" spans="2:5">
       <c r="B286" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C286" t="str">
         <f t="shared" si="4"/>
@@ -7312,7 +7327,7 @@
     </row>
     <row r="287" spans="2:5">
       <c r="B287" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C287" t="str">
         <f t="shared" si="4"/>
@@ -7327,7 +7342,7 @@
     </row>
     <row r="288" spans="2:5">
       <c r="B288" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C288" t="str">
         <f t="shared" si="4"/>
@@ -7342,7 +7357,7 @@
     </row>
     <row r="289" spans="2:5">
       <c r="B289" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C289" t="str">
         <f t="shared" si="4"/>
@@ -7357,7 +7372,7 @@
     </row>
     <row r="290" spans="2:5">
       <c r="B290" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C290" t="str">
         <f t="shared" si="4"/>
@@ -7372,7 +7387,7 @@
     </row>
     <row r="291" spans="2:5">
       <c r="B291" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C291" t="str">
         <f t="shared" si="4"/>
@@ -7387,7 +7402,7 @@
     </row>
     <row r="292" spans="2:5">
       <c r="B292" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C292" t="str">
         <f t="shared" si="4"/>
@@ -7402,7 +7417,7 @@
     </row>
     <row r="293" spans="2:5">
       <c r="B293" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C293" t="str">
         <f t="shared" si="4"/>
@@ -7417,7 +7432,7 @@
     </row>
     <row r="294" spans="2:5">
       <c r="B294" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C294" t="str">
         <f t="shared" si="4"/>
@@ -7432,7 +7447,7 @@
     </row>
     <row r="295" spans="2:5">
       <c r="B295" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C295" t="str">
         <f t="shared" si="4"/>
@@ -7447,7 +7462,7 @@
     </row>
     <row r="296" spans="2:5">
       <c r="B296" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C296" t="str">
         <f t="shared" si="4"/>
@@ -7462,7 +7477,7 @@
     </row>
     <row r="297" spans="2:5">
       <c r="B297" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C297" t="str">
         <f t="shared" si="4"/>
@@ -7477,7 +7492,7 @@
     </row>
     <row r="298" spans="2:5">
       <c r="B298" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C298" t="str">
         <f t="shared" si="4"/>
@@ -7492,7 +7507,7 @@
     </row>
     <row r="299" spans="2:5">
       <c r="B299" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C299" t="str">
         <f t="shared" si="4"/>
@@ -7507,7 +7522,7 @@
     </row>
     <row r="300" spans="2:5">
       <c r="B300" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C300" t="str">
         <f t="shared" si="4"/>
@@ -7522,7 +7537,7 @@
     </row>
     <row r="301" spans="2:5">
       <c r="B301" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C301" t="str">
         <f t="shared" si="4"/>
@@ -7537,7 +7552,7 @@
     </row>
     <row r="302" spans="2:5">
       <c r="B302" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C302" t="str">
         <f t="shared" si="4"/>
@@ -7552,7 +7567,7 @@
     </row>
     <row r="303" spans="2:5">
       <c r="B303" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C303" t="str">
         <f t="shared" si="4"/>
@@ -7567,7 +7582,7 @@
     </row>
     <row r="304" spans="2:5">
       <c r="B304" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C304" t="str">
         <f t="shared" si="4"/>
@@ -7582,7 +7597,7 @@
     </row>
     <row r="305" spans="2:5">
       <c r="B305" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C305" t="str">
         <f t="shared" si="4"/>
@@ -7597,7 +7612,7 @@
     </row>
     <row r="306" spans="2:5">
       <c r="B306" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C306" t="str">
         <f t="shared" si="4"/>
@@ -7612,7 +7627,7 @@
     </row>
     <row r="307" spans="2:5">
       <c r="B307" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C307" t="str">
         <f t="shared" si="4"/>
@@ -7627,7 +7642,7 @@
     </row>
     <row r="308" spans="2:5">
       <c r="B308" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C308" t="str">
         <f t="shared" si="4"/>
@@ -7642,7 +7657,7 @@
     </row>
     <row r="309" spans="2:5">
       <c r="B309" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C309" t="str">
         <f t="shared" si="4"/>
@@ -7657,7 +7672,7 @@
     </row>
     <row r="310" spans="2:5">
       <c r="B310" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C310" t="str">
         <f t="shared" si="4"/>
@@ -7672,7 +7687,7 @@
     </row>
     <row r="311" spans="2:5">
       <c r="B311" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C311" t="str">
         <f t="shared" si="4"/>
@@ -7687,7 +7702,7 @@
     </row>
     <row r="312" spans="2:5">
       <c r="B312" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C312" t="str">
         <f t="shared" si="4"/>
@@ -7702,7 +7717,7 @@
     </row>
     <row r="313" spans="2:5">
       <c r="B313" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C313" t="str">
         <f t="shared" si="4"/>
@@ -7717,7 +7732,7 @@
     </row>
     <row r="314" spans="2:5">
       <c r="B314" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C314" t="str">
         <f t="shared" si="4"/>
@@ -7732,7 +7747,7 @@
     </row>
     <row r="315" spans="2:5">
       <c r="B315" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C315" t="str">
         <f t="shared" si="4"/>
@@ -7747,7 +7762,7 @@
     </row>
     <row r="316" spans="2:5">
       <c r="B316" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C316" t="str">
         <f t="shared" si="4"/>
@@ -7762,7 +7777,7 @@
     </row>
     <row r="317" spans="2:5">
       <c r="B317" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C317" t="str">
         <f t="shared" si="4"/>
@@ -7777,7 +7792,7 @@
     </row>
     <row r="318" spans="2:5">
       <c r="B318" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C318" t="str">
         <f t="shared" si="4"/>
@@ -7792,7 +7807,7 @@
     </row>
     <row r="319" spans="2:5">
       <c r="B319" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C319" t="str">
         <f t="shared" si="4"/>
@@ -7807,7 +7822,7 @@
     </row>
     <row r="320" spans="2:5">
       <c r="B320" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C320" t="str">
         <f t="shared" si="4"/>
@@ -7822,7 +7837,7 @@
     </row>
     <row r="321" spans="2:5">
       <c r="B321" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C321" t="str">
         <f t="shared" si="4"/>
